--- a/public/invoices/CBH-ABR-2026-V2.1.xlsx
+++ b/public/invoices/CBH-ABR-2026-V2.1.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D51"/>
+  <dimension ref="B1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -626,7 +626,7 @@
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>julian@agvmiami.com</t>
+          <t>jclarkson@agvmiami.com</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -807,19 +807,19 @@
     <row r="24" ht="24" customHeight="1">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Optional Add-Ons   ·   Available on request, quoted before execution</t>
+          <t>Optional Add-Ons   ·   Pre-priced overlays, available on request</t>
         </is>
       </c>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Maintenance — Pre-Deployment Activation Refresh</t>
+          <t>Pre-Deployment Refresh</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>A pre-event touch-up pass: paint, hardware, finishes, and lighting recalibration. Quoted to scope at request.</t>
+          <t>Touch-up pass: paint, hardware, finishes, lighting recalibration. Scaled to the asset's condition on intake.</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -832,12 +832,12 @@
     <row r="26" ht="44" customHeight="1">
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Refab — Pre-Deployment Activation Rebrand</t>
+          <t>Pre-Deployment Rebrand</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Graphics, wraps, or finish refresh aligned with a new campaign or partnership. Quoted to scope at request.</t>
+          <t>Graphics, wraps, or finish refresh aligned with a new campaign or partnership. Designed at the front end.</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
@@ -847,238 +847,318 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="5" t="inlineStr">
+    <row r="27" ht="44" customHeight="1">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>On-Site Show-Day Coverage</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>AGV producer or specialized tech on the ground during show days — refresh, repair, or in-window punch-list response.</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>from $850
+per day</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Change Orders   ·   Commercial mechanics — bundle savings, pass-through, overflow storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Calendar Bundle Discount</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>4+ events committed inside a single 12-month window unlock 6–10% off per-activation logistics. Stacks on the rate card.</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>6–10%
+stacks on rate card</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="1">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Travel Pass-Through (Above Cap)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Travel or lodging beyond the per-activation Travel &amp; Lodging line cap bills at cost with receipts on written authorization.</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>At cost
+with receipts</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="1">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Additional Storage (Overflow Pallets)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Storage beyond the standard footprint — overflow pallets, additional environmental control — bills monthly per pallet.</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>$400
+per pallet / month</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>ABBEY ROAD · APPLIED COMPOSITION</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="8" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Build &amp; Strike — Logistics</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Asymmetric route absorbed inside the baseline.</t>
         </is>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D34" s="11" t="n">
         <v>4500</v>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="8" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Build &amp; Strike — Labor (Local Hires)</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr"/>
-      <c r="D30" s="11" t="n">
+      <c r="C35" s="9" t="inlineStr"/>
+      <c r="D35" s="11" t="n">
         <v>1800</v>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="8" t="inlineStr">
+    <row r="36" ht="30" customHeight="1">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Build &amp; Strike — Travel &amp; Lodging (1–2 AGV Crew)</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr"/>
-      <c r="D31" s="11" t="n">
+      <c r="C36" s="9" t="inlineStr"/>
+      <c r="D36" s="11" t="n">
         <v>2500</v>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="8" t="inlineStr">
+    <row r="37" ht="30" customHeight="1">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Plants — Foliage Rental</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>Per activation instance.</t>
         </is>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D37" s="11" t="n">
         <v>1200</v>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="8" t="inlineStr">
+    <row r="38" ht="30" customHeight="1">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Lighting — Upgrade + Routine Maintenance</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Year-1 only — covers the calendar going forward.</t>
         </is>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D38" s="11" t="n">
         <v>4500</v>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="12" t="inlineStr">
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>Per activation $8,800   ·   Upgrades $5,700</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr"/>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="B35" s="14" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr"/>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>ABBEY ROAD ENGAGEMENT NET</t>
         </is>
       </c>
-      <c r="D35" s="15" t="n">
+      <c r="D40" s="15" t="n">
         <v>14500</v>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="5" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>2026 CALENDAR — PER-EVENT PROJECTION</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="B38" s="8" t="inlineStr">
+    <row r="43" ht="24" customHeight="1">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Abbey Road on the River</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>May 21–25, Jeffersonville, IN  ·  1,200 mi · out-of-market  ·  incl. lighting upgrade</t>
         </is>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D43" s="11" t="n">
         <v>14500</v>
       </c>
     </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="B39" s="8" t="inlineStr">
+    <row r="44" ht="24" customHeight="1">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Minnesota Yacht Club Festival</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>Jul 17–19, St. Paul, MN  ·  1,800 mi · out-of-market  ·  per-activation + plants</t>
         </is>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D44" s="11" t="n">
         <v>10000</v>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="B40" s="8" t="inlineStr">
+    <row r="45" ht="24" customHeight="1">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>North Carolina Folk Festival</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>Sept 18–20, Greensboro, NC  ·  800 mi · out-of-market  ·  per-activation + plants</t>
         </is>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D45" s="11" t="n">
         <v>10000</v>
       </c>
     </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="B41" s="8" t="inlineStr">
+    <row r="46" ht="24" customHeight="1">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Fin Fest</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>Nov 13–14, St. Petersburg, FL  ·  270 mi · local market  ·  no lodging line, day trips</t>
         </is>
       </c>
-      <c r="D41" s="11" t="n">
+      <c r="D46" s="11" t="n">
         <v>6500</v>
       </c>
     </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="12" t="inlineStr">
+    <row r="47" ht="22" customHeight="1">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>Annual production — 4 events + year-1 lighting upgrade</t>
         </is>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="D47" s="16" t="n">
         <v>41000</v>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="17" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>+ Storage at $1,500/month rolling — billed monthly between deployments.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>PAYMENT TERMS</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="70" customHeight="1">
-      <c r="B46" s="6" t="inlineStr">
+    <row r="51" ht="70" customHeight="1">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>50% deposit ($7,250) due upon Client's written approval of this Scope of Work (Proposal execution). 50% balance ($7,250) due on or before May 12, 2026 (pre-event walkthrough date). Payment exclusively via ACH electronic transfer or domestic wire transfer; ACH/wire details issued directly to the Client billing contact upon SoW approval. Reference CBH-ABR-2026 V2.1 on all remittances.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>CANCELLATION &amp; CHANGE ORDERS</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="B49" s="6" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Full refund if cancelled before May 5. 50% refund between May 5 — May 12. No refund after May 12 (truck, driver, plants, and lighting locked). Anything added — additional crew, on-site coverage, refresh, rebrand — is quoted as a written change order before execution. Nothing billed that wasn't signed.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="36" customHeight="1">
-      <c r="B51" s="18" t="inlineStr">
-        <is>
-          <t>AGV Miami, LLC  ·  julian@agvmiami.com  ·  This invoice is issued in connection with proposal CBH-ABR-2026 V2.1 and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Cornbread Hemp.</t>
+    <row r="56" ht="36" customHeight="1">
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>AGV Miami, LLC  ·  jclarkson@agvmiami.com  ·  This invoice is issued in connection with proposal CBH-ABR-2026 V2.1 and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Cornbread Hemp.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B47:C47"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B42:C42"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B56:D56"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B43:D43"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B48:D48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
